--- a/research/traditional_assets/database/data/hong_kong/hong_kong_broadcasting.xlsx
+++ b/research/traditional_assets/database/data/hong_kong/hong_kong_broadcasting.xlsx
@@ -588,34 +588,34 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.0241</v>
+        <v>-0.06059999999999999</v>
       </c>
       <c r="G2">
-        <v>-0.1332199546485261</v>
+        <v>-0.09449819719332832</v>
       </c>
       <c r="H2">
-        <v>-0.1425563422647971</v>
+        <v>-0.1079868226505149</v>
       </c>
       <c r="I2">
-        <v>-0.2166474320606532</v>
+        <v>-0.1720353100208882</v>
       </c>
       <c r="J2">
-        <v>-0.2166474320606532</v>
+        <v>-0.1720353100208882</v>
       </c>
       <c r="K2">
-        <v>-176.1</v>
+        <v>-164.7</v>
       </c>
       <c r="L2">
-        <v>-0.2037345550465084</v>
+        <v>-0.2136131358460222</v>
       </c>
       <c r="M2">
-        <v>0.125</v>
+        <v>0</v>
       </c>
       <c r="N2">
-        <v>0.0002222222222222222</v>
+        <v>0</v>
       </c>
       <c r="O2">
-        <v>-0.000709823963657013</v>
+        <v>-0</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -627,79 +627,76 @@
         <v>-0</v>
       </c>
       <c r="S2">
-        <v>0.125</v>
-      </c>
-      <c r="T2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U2">
-        <v>258.82</v>
+        <v>280.78</v>
       </c>
       <c r="V2">
-        <v>0.4601244444444444</v>
+        <v>0.759891745602165</v>
       </c>
       <c r="W2">
-        <v>-0.126605504587156</v>
+        <v>-0.1814946619217082</v>
       </c>
       <c r="X2">
-        <v>0.1227041586885902</v>
+        <v>0.1001113104088828</v>
       </c>
       <c r="Y2">
-        <v>-0.2493096632757461</v>
+        <v>-0.281605972330591</v>
       </c>
       <c r="Z2">
-        <v>0.5285112510795137</v>
+        <v>0.6029489820110079</v>
       </c>
       <c r="AA2">
-        <v>-0.09578741373982902</v>
+        <v>-0.04651484651115782</v>
       </c>
       <c r="AB2">
-        <v>0.09359439724586231</v>
+        <v>0.07718693166849017</v>
       </c>
       <c r="AC2">
-        <v>-0.1893818109856913</v>
+        <v>-0.1217494203376491</v>
       </c>
       <c r="AD2">
-        <v>475</v>
+        <v>428.71</v>
       </c>
       <c r="AE2">
-        <v>1.261871879730889</v>
+        <v>3.168323661526101</v>
       </c>
       <c r="AF2">
-        <v>476.2618718797309</v>
+        <v>431.8783236615261</v>
       </c>
       <c r="AG2">
-        <v>217.4418718797309</v>
+        <v>151.0983236615261</v>
       </c>
       <c r="AH2">
-        <v>0.4584899434341898</v>
+        <v>0.5389193978797163</v>
       </c>
       <c r="AI2">
-        <v>0.2745718556373026</v>
+        <v>0.2907726563980644</v>
       </c>
       <c r="AJ2">
-        <v>0.2787924071260288</v>
+        <v>0.2902397429918824</v>
       </c>
       <c r="AK2">
-        <v>0.1473441094429093</v>
+        <v>0.1254450261102945</v>
       </c>
       <c r="AL2">
-        <v>17.83</v>
+        <v>23.27</v>
       </c>
       <c r="AM2">
-        <v>-8.899999999999999</v>
+        <v>2.719000000000001</v>
       </c>
       <c r="AN2">
-        <v>-3.742809865258845</v>
+        <v>-5.13677374519225</v>
       </c>
       <c r="AO2">
-        <v>-10.52938867077959</v>
+        <v>-5.711645896003438</v>
       </c>
       <c r="AP2">
-        <v>-1.713354911982751</v>
+        <v>-1.81044972575188</v>
       </c>
       <c r="AQ2">
-        <v>21.09426966292135</v>
+        <v>-48.88194189040086</v>
       </c>
     </row>
     <row r="3">
@@ -719,34 +716,34 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.0142</v>
+        <v>0.07429999999999999</v>
       </c>
       <c r="G3">
-        <v>-0.2232704402515723</v>
+        <v>-0.3542600896860987</v>
       </c>
       <c r="H3">
-        <v>-0.2232704402515723</v>
+        <v>-0.3542600896860987</v>
       </c>
       <c r="I3">
-        <v>-0.1004716981132075</v>
+        <v>-0.3598654708520179</v>
       </c>
       <c r="J3">
-        <v>-0.1004716981132075</v>
+        <v>-0.3598654708520179</v>
       </c>
       <c r="K3">
-        <v>-32.2</v>
+        <v>-15.3</v>
       </c>
       <c r="L3">
-        <v>-5.062893081761007</v>
+        <v>-1.715246636771301</v>
       </c>
       <c r="M3">
-        <v>0.091</v>
+        <v>-0</v>
       </c>
       <c r="N3">
-        <v>0.0007303370786516854</v>
+        <v>-0</v>
       </c>
       <c r="O3">
-        <v>-0.002826086956521739</v>
+        <v>0</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -758,79 +755,76 @@
         <v>0</v>
       </c>
       <c r="S3">
-        <v>0.091</v>
-      </c>
-      <c r="T3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U3">
-        <v>1.72</v>
+        <v>0.28</v>
       </c>
       <c r="V3">
-        <v>0.01380417335473515</v>
+        <v>0.008641975308641976</v>
       </c>
       <c r="W3">
-        <v>-0.3522975929978118</v>
+        <v>-0.1814946619217082</v>
       </c>
       <c r="X3">
-        <v>0.09797742496362317</v>
+        <v>0.08470683597306462</v>
       </c>
       <c r="Y3">
-        <v>-0.450275017961435</v>
+        <v>-0.2662014978947728</v>
       </c>
       <c r="Z3">
-        <v>0.04327708219923788</v>
+        <v>0.08670295489891136</v>
       </c>
       <c r="AA3">
-        <v>-0.004348121937942297</v>
+        <v>-0.03120139968895801</v>
       </c>
       <c r="AB3">
-        <v>0.09198753949028129</v>
+        <v>0.07718693166849017</v>
       </c>
       <c r="AC3">
-        <v>-0.09633566142822358</v>
+        <v>-0.1083883313574482</v>
       </c>
       <c r="AD3">
-        <v>20.3</v>
+        <v>9.01</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>20.3</v>
+        <v>9.01</v>
       </c>
       <c r="AG3">
-        <v>18.58</v>
+        <v>8.73</v>
       </c>
       <c r="AH3">
-        <v>0.1400966183574879</v>
+        <v>0.2175802946148273</v>
       </c>
       <c r="AI3">
-        <v>0.1720338983050848</v>
+        <v>0.08357295241628791</v>
       </c>
       <c r="AJ3">
-        <v>0.1297667271965358</v>
+        <v>0.2122538293216631</v>
       </c>
       <c r="AK3">
-        <v>0.1597867217062264</v>
+        <v>0.08118664558727798</v>
       </c>
       <c r="AL3">
-        <v>3.03</v>
+        <v>1.98</v>
       </c>
       <c r="AM3">
-        <v>3.03</v>
+        <v>1.979</v>
       </c>
       <c r="AN3">
-        <v>-31.71875</v>
+        <v>-2.815625</v>
       </c>
       <c r="AO3">
-        <v>-0.2108910891089109</v>
+        <v>-1.621212121212121</v>
       </c>
       <c r="AP3">
-        <v>-29.03125</v>
+        <v>-2.728125</v>
       </c>
       <c r="AQ3">
-        <v>-0.2108910891089109</v>
+        <v>-1.622031328954017</v>
       </c>
     </row>
     <row r="4">
@@ -841,7 +835,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Television Broadcasts Limited (SEHK:511)</t>
+          <t>Phoenix Media Investment (Holdings) Limited (SEHK:2008)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -850,25 +844,25 @@
         </is>
       </c>
       <c r="D4">
-        <v>-0.0405</v>
+        <v>-0.0882</v>
       </c>
       <c r="G4">
-        <v>-0.1241917250734795</v>
+        <v>-0.06011252591057151</v>
       </c>
       <c r="H4">
-        <v>-0.1424372597784309</v>
+        <v>-0.06011252591057151</v>
       </c>
       <c r="I4">
-        <v>-0.2102645263395885</v>
+        <v>-0.06761227341517685</v>
       </c>
       <c r="J4">
-        <v>-0.2102645263395885</v>
+        <v>-0.06761227341517685</v>
       </c>
       <c r="K4">
-        <v>-74.90000000000001</v>
+        <v>-23.1</v>
       </c>
       <c r="L4">
-        <v>-0.1693420755143568</v>
+        <v>-0.06840390879478828</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -892,73 +886,73 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>116</v>
+        <v>180.1</v>
       </c>
       <c r="V4">
-        <v>0.5595754944524843</v>
+        <v>1.1270337922403</v>
       </c>
       <c r="W4">
-        <v>-0.1199935917975008</v>
+        <v>-0.05006501950585176</v>
       </c>
       <c r="X4">
-        <v>0.1511727012260334</v>
+        <v>0.1001113104088828</v>
       </c>
       <c r="Y4">
-        <v>-0.2711662930235342</v>
+        <v>-0.1501763299147346</v>
       </c>
       <c r="Z4">
-        <v>0.4555566999691008</v>
+        <v>0.6879645390050838</v>
       </c>
       <c r="AA4">
-        <v>-0.09578741373982902</v>
+        <v>-0.04651484651115782</v>
       </c>
       <c r="AB4">
-        <v>0.09359439724586231</v>
+        <v>0.07523457382649128</v>
       </c>
       <c r="AC4">
-        <v>-0.1893818109856913</v>
+        <v>-0.1217494203376491</v>
       </c>
       <c r="AD4">
-        <v>287.3</v>
+        <v>120.4</v>
       </c>
       <c r="AE4">
-        <v>0</v>
+        <v>3.168323661526101</v>
       </c>
       <c r="AF4">
-        <v>287.3</v>
+        <v>123.5683236615261</v>
       </c>
       <c r="AG4">
-        <v>171.3</v>
+        <v>-56.53167633847389</v>
       </c>
       <c r="AH4">
-        <v>0.5808734330772342</v>
+        <v>0.4360696427351008</v>
       </c>
       <c r="AI4">
-        <v>0.3446497120921306</v>
+        <v>0.1822358003604489</v>
       </c>
       <c r="AJ4">
-        <v>0.4524564183835182</v>
+        <v>-0.5474251380681165</v>
       </c>
       <c r="AK4">
-        <v>0.2387123745819398</v>
+        <v>-0.1135246433403644</v>
       </c>
       <c r="AL4">
-        <v>9.16</v>
+        <v>5.29</v>
       </c>
       <c r="AM4">
-        <v>-8.039999999999999</v>
+        <v>-1.26</v>
       </c>
       <c r="AN4">
-        <v>-5.431001890359169</v>
+        <v>-15.12752858399297</v>
       </c>
       <c r="AO4">
-        <v>-10.1528384279476</v>
+        <v>-4.366729678638942</v>
       </c>
       <c r="AP4">
-        <v>-3.238185255198488</v>
+        <v>7.102861708565635</v>
       </c>
       <c r="AQ4">
-        <v>11.56716417910448</v>
+        <v>18.33333333333334</v>
       </c>
     </row>
     <row r="5">
@@ -969,7 +963,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Phoenix Media Investment (Holdings) Limited (SEHK:2008)</t>
+          <t>Television Broadcasts Limited (SEHK:511)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -978,34 +972,34 @@
         </is>
       </c>
       <c r="D5">
-        <v>-0.0241</v>
+        <v>-0.06059999999999999</v>
       </c>
       <c r="G5">
-        <v>-0.1414481597305749</v>
+        <v>-0.1163996229971725</v>
       </c>
       <c r="H5">
-        <v>-0.1414481597305749</v>
+        <v>-0.1409048067860509</v>
       </c>
       <c r="I5">
-        <v>-0.2252162000864714</v>
+        <v>-0.2511781338360038</v>
       </c>
       <c r="J5">
-        <v>-0.2252162000864714</v>
+        <v>-0.2511781338360038</v>
       </c>
       <c r="K5">
-        <v>-69</v>
+        <v>-126.3</v>
       </c>
       <c r="L5">
-        <v>-0.1659850853981236</v>
+        <v>-0.2975966069745523</v>
       </c>
       <c r="M5">
-        <v>0.034</v>
+        <v>-0</v>
       </c>
       <c r="N5">
-        <v>0.0001474414570685169</v>
+        <v>-0</v>
       </c>
       <c r="O5">
-        <v>-0.0004927536231884058</v>
+        <v>0</v>
       </c>
       <c r="P5">
         <v>-0</v>
@@ -1017,79 +1011,76 @@
         <v>0</v>
       </c>
       <c r="S5">
-        <v>0.034</v>
-      </c>
-      <c r="T5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U5">
-        <v>141.1</v>
+        <v>100.4</v>
       </c>
       <c r="V5">
-        <v>0.6118820468343452</v>
+        <v>0.5662718556119571</v>
       </c>
       <c r="W5">
-        <v>-0.126605504587156</v>
+        <v>-0.2408007626310772</v>
       </c>
       <c r="X5">
-        <v>0.1227041586885902</v>
+        <v>0.1285705034138964</v>
       </c>
       <c r="Y5">
-        <v>-0.2493096632757461</v>
+        <v>-0.3693712660449736</v>
       </c>
       <c r="Z5">
-        <v>0.8031269255080887</v>
+        <v>0.6195620437956204</v>
       </c>
       <c r="AA5">
-        <v>-0.1808771943500623</v>
+        <v>-0.1556204379562044</v>
       </c>
       <c r="AB5">
-        <v>0.09818327952554387</v>
+        <v>0.08317703263420462</v>
       </c>
       <c r="AC5">
-        <v>-0.2790604738756062</v>
+        <v>-0.238797470590409</v>
       </c>
       <c r="AD5">
-        <v>167.4</v>
+        <v>299.3</v>
       </c>
       <c r="AE5">
-        <v>1.261871879730889</v>
+        <v>0</v>
       </c>
       <c r="AF5">
-        <v>168.6618718797309</v>
+        <v>299.3</v>
       </c>
       <c r="AG5">
-        <v>27.56187187973089</v>
+        <v>198.9</v>
       </c>
       <c r="AH5">
-        <v>0.4224342061155709</v>
+        <v>0.6279899286613513</v>
       </c>
       <c r="AI5">
-        <v>0.2154151791259111</v>
+        <v>0.4279382327709465</v>
       </c>
       <c r="AJ5">
-        <v>0.1067619772007659</v>
+        <v>0.5287081339712918</v>
       </c>
       <c r="AK5">
-        <v>0.04294050338122484</v>
+        <v>0.3320534223706177</v>
       </c>
       <c r="AL5">
-        <v>5.64</v>
+        <v>16</v>
       </c>
       <c r="AM5">
-        <v>-3.89</v>
+        <v>2</v>
       </c>
       <c r="AN5">
-        <v>-2.281586479487529</v>
+        <v>-4.139695712309821</v>
       </c>
       <c r="AO5">
-        <v>-16.68439716312057</v>
+        <v>-6.6625</v>
       </c>
       <c r="AP5">
-        <v>-0.3756558795111202</v>
+        <v>-2.75103734439834</v>
       </c>
       <c r="AQ5">
-        <v>24.19023136246787</v>
+        <v>-53.3</v>
       </c>
     </row>
   </sheetData>
